--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_prebrut_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_prebrut_a_2021.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:20</t>
+    <t xml:space="preserve">2026-09-24 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -640,7 +640,7 @@
         <v>0.21</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -654,7 +654,7 @@
         <v>0.16</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         <v>0.14</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
@@ -679,10 +679,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
